--- a/result/case/case3.xlsx
+++ b/result/case/case3.xlsx
@@ -634,7 +634,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -667,14 +667,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>npp</t>
+          <t>pre</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.7906236204443422</v>
       </c>
       <c r="D2">
-        <v>-0</v>
+        <v>9.574992216403358E-321</v>
       </c>
     </row>
     <row r="3">
@@ -685,32 +685,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pre</t>
+          <t>tem</t>
         </is>
       </c>
       <c r="C3">
-        <v>0.7906236204443422</v>
+        <v>0.6767460761540719</v>
       </c>
       <c r="D3">
-        <v>9.574992216403358E-321</v>
+        <v>2.459234976177667E-201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>npp</t>
+          <t>pre</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tem</t>
+          <t>npp</t>
         </is>
       </c>
       <c r="C4">
-        <v>0.6767460761540719</v>
+        <v>0.7906236204443422</v>
       </c>
       <c r="D4">
-        <v>2.459234976177667E-201</v>
+        <v>3.191664072134453E-321</v>
       </c>
     </row>
     <row r="5">
@@ -721,104 +721,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>npp</t>
+          <t>tem</t>
         </is>
       </c>
       <c r="C5">
-        <v>0.7906236204443422</v>
+        <v>0.7834559178342438</v>
       </c>
       <c r="D5">
-        <v>3.191664072134453E-321</v>
+        <v>2.801567142578441E-311</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pre</t>
+          <t>tem</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pre</t>
+          <t>npp</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.6767460761540719</v>
       </c>
       <c r="D6">
-        <v>-0</v>
+        <v>2.459234976177667E-201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pre</t>
+          <t>tem</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tem</t>
+          <t>pre</t>
         </is>
       </c>
       <c r="C7">
         <v>0.7834559178342438</v>
       </c>
       <c r="D7">
-        <v>2.801567142578441E-311</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tem</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>npp</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.6767460761540719</v>
-      </c>
-      <c r="D8">
-        <v>2.459234976177667E-201</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tem</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.7834559178342438</v>
-      </c>
-      <c r="D9">
         <v>1.40078357128922E-311</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tem</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>tem</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/result/case/case3.xlsx
+++ b/result/case/case3.xlsx
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.8384087791495199</v>
+        <v>0.6088477366255144</v>
       </c>
       <c r="D2">
-        <v>3.023332468965753E-57</v>
+        <v>8.929334696363851E-05</v>
       </c>
     </row>
     <row r="3">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.7937997256515775</v>
+        <v>0.5383539094650206</v>
       </c>
       <c r="D3">
-        <v>1.076713924473735E-36</v>
+        <v>0.1686403908193261</v>
       </c>
     </row>
     <row r="4">
@@ -427,10 +427,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.8353772290809328</v>
+        <v>0.6401508916323732</v>
       </c>
       <c r="D4">
-        <v>1.068290842990452E-55</v>
+        <v>2.548677130963522E-07</v>
       </c>
     </row>
     <row r="5">
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.8208367626886145</v>
+        <v>0.6113991769547326</v>
       </c>
       <c r="D5">
-        <v>5.905870373668247E-48</v>
+        <v>4.810112946444046E-05</v>
       </c>
     </row>
     <row r="6">
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.8667489711934157</v>
+        <v>0.6800274348422497</v>
       </c>
       <c r="D6">
-        <v>1.22386764057911E-77</v>
+        <v>1.305996581422433E-11</v>
       </c>
     </row>
     <row r="7">
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.8443621399176955</v>
+        <v>0.6381344307270234</v>
       </c>
       <c r="D7">
-        <v>2.164120088290421E-61</v>
+        <v>3.699710962600703E-07</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.4879351292466522</v>
+        <v>0.4810587174448395</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.3601139284574653</v>
+        <v>0.3463673747100529</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.3559751734635753</v>
+        <v>0.339228267022784</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.2480723966409923</v>
+        <v>0.1578902230355661</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>7.818528047209838E-10</v>
       </c>
     </row>
     <row r="6">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.3452197103973743</v>
+        <v>0.3730429444426802</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.3482702602736988</v>
+        <v>0.3461900416026312</v>
       </c>
       <c r="D7">
         <v>0</v>

--- a/result/case/case3.xlsx
+++ b/result/case/case3.xlsx
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.6088477366255144</v>
+        <v>0.2181795918367347</v>
       </c>
       <c r="D2">
-        <v>8.929334696363851E-05</v>
+        <v>4.990672434241546E-48</v>
       </c>
     </row>
     <row r="3">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.5383539094650206</v>
+        <v>0.1876816326530612</v>
       </c>
       <c r="D3">
-        <v>0.1686403908193261</v>
+        <v>7.390330900445726E-67</v>
       </c>
     </row>
     <row r="4">
@@ -427,10 +427,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.6401508916323732</v>
+        <v>0.3869142857142857</v>
       </c>
       <c r="D4">
-        <v>2.548677130963522E-07</v>
+        <v>1.716557997522749E-06</v>
       </c>
     </row>
     <row r="5">
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.6113991769547326</v>
+        <v>0.3799673469387755</v>
       </c>
       <c r="D5">
-        <v>4.810112946444046E-05</v>
+        <v>3.234267975195473E-07</v>
       </c>
     </row>
     <row r="6">
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.6800274348422497</v>
+        <v>0.3206775510204082</v>
       </c>
       <c r="D6">
-        <v>1.305996581422433E-11</v>
+        <v>1.429894972415768E-15</v>
       </c>
     </row>
     <row r="7">
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.6381344307270234</v>
+        <v>0.292669387755102</v>
       </c>
       <c r="D7">
-        <v>3.699710962600703E-07</v>
+        <v>2.796328581440632E-21</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.4810587174448395</v>
+        <v>0.5127123623584123</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.3463673747100529</v>
+        <v>0.4407668662231769</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.339228267022784</v>
+        <v>0.3467850703613701</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.1578902230355661</v>
+        <v>0.3345758759930962</v>
       </c>
       <c r="D5">
-        <v>7.818528047209838E-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.3730429444426802</v>
+        <v>0.4617923319911552</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.3461900416026312</v>
+        <v>0.4242145571475958</v>
       </c>
       <c r="D7">
         <v>0</v>

--- a/result/case/case3.xlsx
+++ b/result/case/case3.xlsx
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2181795918367347</v>
+        <v>0.2439832341806382</v>
       </c>
       <c r="D2">
-        <v>4.990672434241546E-48</v>
+        <v>1.896606261923489E-17</v>
       </c>
     </row>
     <row r="3">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.1876816326530612</v>
+        <v>0.2071727961060033</v>
       </c>
       <c r="D3">
-        <v>7.390330900445726E-67</v>
+        <v>1.371208579800059E-25</v>
       </c>
     </row>
     <row r="4">
@@ -427,10 +427,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.3869142857142857</v>
+        <v>0.4304691725256896</v>
       </c>
       <c r="D4">
-        <v>1.716557997522749E-06</v>
+        <v>0.04764654115079872</v>
       </c>
     </row>
     <row r="5">
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.3799673469387755</v>
+        <v>0.4326325040562466</v>
       </c>
       <c r="D5">
-        <v>3.234267975195473E-07</v>
+        <v>0.05583347285484098</v>
       </c>
     </row>
     <row r="6">
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.3206775510204082</v>
+        <v>0.3261898323418064</v>
       </c>
       <c r="D6">
-        <v>1.429894972415768E-15</v>
+        <v>1.470219394014243E-07</v>
       </c>
     </row>
     <row r="7">
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.292669387755102</v>
+        <v>0.2761289886425095</v>
       </c>
       <c r="D7">
-        <v>2.796328581440632E-21</v>
+        <v>5.22770828231353E-13</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.5127123623584123</v>
+        <v>0.8276760656389834</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.4407668662231769</v>
+        <v>0.7957231689455366</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.3467850703613701</v>
+        <v>0.707747799985694</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.3345758759930962</v>
+        <v>0.6484832421018795</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.4617923319911552</v>
+        <v>0.7619731473471065</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.4242145571475958</v>
+        <v>0.7994555462466125</v>
       </c>
       <c r="D7">
         <v>0</v>

--- a/result/case/case3.xlsx
+++ b/result/case/case3.xlsx
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2439832341806382</v>
+        <v>0.239742883379247</v>
       </c>
       <c r="D2">
-        <v>1.896606261923489E-17</v>
+        <v>1.57180651321647E-17</v>
       </c>
     </row>
     <row r="3">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.2071727961060033</v>
+        <v>0.2060238751147842</v>
       </c>
       <c r="D3">
-        <v>1.371208579800059E-25</v>
+        <v>6.525043626699835E-25</v>
       </c>
     </row>
     <row r="4">
@@ -427,10 +427,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.4304691725256896</v>
+        <v>0.4287970615243343</v>
       </c>
       <c r="D4">
-        <v>0.04764654115079872</v>
+        <v>0.0470687916497408</v>
       </c>
     </row>
     <row r="5">
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.4326325040562466</v>
+        <v>0.4322130394857668</v>
       </c>
       <c r="D5">
-        <v>0.05583347285484098</v>
+        <v>0.05956945786229592</v>
       </c>
     </row>
     <row r="6">
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.3261898323418064</v>
+        <v>0.3222038567493113</v>
       </c>
       <c r="D6">
-        <v>1.470219394014243E-07</v>
+        <v>1.261609306669625E-07</v>
       </c>
     </row>
     <row r="7">
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.2761289886425095</v>
+        <v>0.2725068870523416</v>
       </c>
       <c r="D7">
-        <v>5.22770828231353E-13</v>
+        <v>5.041517325850549E-13</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.8276760656389834</v>
+        <v>0.8324397811656905</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.7957231689455366</v>
+        <v>0.7989642933404404</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.707747799985694</v>
+        <v>0.7143327286488832</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2.465172120603125E-234</v>
       </c>
     </row>
     <row r="5">
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.6484832421018795</v>
+        <v>0.6559515226195394</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4.110980962179658E-185</v>
       </c>
     </row>
     <row r="6">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.7619731473471065</v>
+        <v>0.7672520290787253</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4.427251241059769E-291</v>
       </c>
     </row>
     <row r="7">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.7994555462466125</v>
+        <v>0.8053771235694317</v>
       </c>
       <c r="D7">
         <v>0</v>

--- a/result/case/case3.xlsx
+++ b/result/case/case3.xlsx
@@ -370,7 +370,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">

--- a/result/case/case3.xlsx
+++ b/result/case/case3.xlsx
@@ -570,7 +570,7 @@
         <v>0.7143327286488832</v>
       </c>
       <c r="D4">
-        <v>2.465172120603125E-234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         <v>0.6559515226195394</v>
       </c>
       <c r="D5">
-        <v>4.110980962179658E-185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -606,7 +606,7 @@
         <v>0.7672520290787253</v>
       </c>
       <c r="D6">
-        <v>4.427251241059769E-291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
